--- a/Pruebas calificadas/COLEGIO SAN VICENTE-702_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SAN VICENTE-702_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -5112,7 +5040,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -5365,7 +5289,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -5618,7 +5538,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -5871,7 +5787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6108,11 +6024,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -6120,7 +6032,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6357,11 +6269,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -6369,7 +6277,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6610,11 +6518,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -6622,7 +6526,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6863,11 +6767,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -6875,7 +6775,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7116,11 +7016,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -7128,7 +7024,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7369,11 +7265,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -7381,7 +7273,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7622,11 +7514,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -7634,7 +7522,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7875,11 +7763,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -7887,7 +7771,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8128,11 +8012,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -8140,7 +8020,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8381,11 +8261,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -8393,7 +8269,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,11 +8510,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -8646,7 +8518,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8883,11 +8755,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -8895,7 +8763,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9136,11 +9004,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -9148,7 +9012,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9389,11 +9253,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -9401,7 +9261,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9642,11 +9502,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -9654,7 +9510,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9895,11 +9751,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -9907,7 +9759,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10148,11 +10000,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -10160,7 +10008,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10401,11 +10249,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -10413,7 +10257,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10654,11 +10498,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -10666,7 +10506,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10907,11 +10747,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -10919,7 +10755,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11160,11 +10996,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -11172,7 +11004,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11413,11 +11245,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -11425,7 +11253,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -11670,7 +11494,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11903,11 +11727,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -11915,7 +11735,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12156,11 +11976,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -12168,7 +11984,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12409,11 +12225,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -12421,7 +12233,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12658,11 +12470,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -12670,7 +12478,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12911,11 +12719,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -12923,7 +12727,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13164,11 +12968,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -13176,7 +12976,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13417,11 +13217,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -13429,7 +13225,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13670,11 +13466,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -13682,7 +13474,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13895,11 +13687,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -13907,7 +13695,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14148,11 +13936,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -14160,7 +13944,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14401,11 +14185,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -14413,7 +14193,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14654,11 +14434,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -14666,7 +14442,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14907,11 +14683,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -14919,7 +14691,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15160,11 +14932,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -15172,7 +14940,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15413,11 +15181,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -15425,7 +15189,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15666,11 +15430,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -15678,7 +15438,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15919,11 +15679,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -15931,7 +15687,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16172,11 +15928,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -16184,7 +15936,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16425,11 +16177,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -16437,7 +16185,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16678,11 +16426,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -16690,7 +16434,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16931,11 +16675,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -16943,7 +16683,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17184,11 +16924,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -17196,7 +16932,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17437,11 +17173,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -17449,7 +17181,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17690,11 +17422,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -17702,7 +17430,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17943,11 +17671,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -17955,7 +17679,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18196,11 +17920,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -18208,7 +17928,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18449,11 +18169,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -18461,7 +18177,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18702,11 +18418,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -18714,7 +18426,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18955,11 +18667,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -18967,7 +18675,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19208,11 +18916,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -19220,7 +18924,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19461,11 +19165,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -19473,7 +19173,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19714,11 +19414,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -19726,7 +19422,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19967,11 +19663,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -19979,7 +19671,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20220,11 +19912,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -20232,7 +19920,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20473,11 +20161,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -20485,7 +20169,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20726,11 +20410,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -20738,7 +20418,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -20979,11 +20659,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -20991,7 +20667,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21232,11 +20908,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -21244,7 +20916,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -21485,11 +21157,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -21497,7 +21165,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -21738,11 +21406,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -21750,7 +21414,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -21991,11 +21655,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -22003,7 +21663,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -22244,11 +21904,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -22256,7 +21912,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -22497,11 +22153,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -22509,7 +22161,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -22750,11 +22402,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -22762,7 +22410,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -23003,11 +22651,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -23015,7 +22659,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -23256,11 +22900,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -23268,7 +22908,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -23509,11 +23149,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -23521,7 +23157,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -23762,11 +23398,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
           <t>111001098825</t>
@@ -23774,7 +23406,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SAN VICENTE (IED)</t>
+          <t>COLEGIO SAN VICENTE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
